--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/28 Day Follow Up Form (CPH) - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/28 Day Follow Up Form (CPH) - metadata.xlsx
@@ -985,7 +985,7 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other Hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
+        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1529,7 +1529,7 @@
         <v>$CauseOfDeatKnow = 'True'</v>
       </c>
       <c r="N17" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Feeding difficulty"},{"value":"DUM","valueLabel":"Dumped baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Hypoglycaemia risk"},{"value":"HIE","valueLabel":"Birth Asphyxia/ Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"PMA","valueLabel":"Meconium aspiration (suspected)"},{"value":"MecEx","valueLabel":"Meconium exposure (not symptomatic)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"SEPS","valueLabel":"Neonatal Sepsis"},{"value":"Risk","valueLabel":"Risk factors for sepsis (asymptomatic baby)"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"OTH","valueLabel":"Other"},{"value":"Mac","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with RD"},{"value":"DJ","valueLabel":"Pathological Jaundice"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Feeding difficulty"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Hypoglycaemia risk"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"PMA","valueLabel":"Meconium aspiration (suspected)"},{"value":"MecEx","valueLabel":"Meconium exposure (not symptomatic)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"SEPS","valueLabel":"Neonatal Sepsis"},{"value":"Risk","valueLabel":"Risk factors for sepsis (asymptomatic baby)"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"OTH","valueLabel":"Other"},{"value":"Mac","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Respiratory Distress (term baby)"},{"value":"DJ","valueLabel":"Jaundice (pathological)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"}]</v>
       </c>
       <c r="O17" t="str">
         <v>$BabyPass = 'ContYes'</v>
